--- a/excel-files/TAGUIG_PATEROS/STAND ALONE SHS WITHIN TAGUIG INTEGRATED SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/STAND ALONE SHS WITHIN TAGUIG INTEGRATED SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29517713-82C8-446F-A3EC-D219225304F2}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DA68E4C-253E-4148-A623-D6CD5ADD460A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3491,7 +3491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3528,7 +3528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:8" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3628,12 +3628,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:8" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3733,12 +3733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:8" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3868,7 +3868,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:8" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4058,7 +4058,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4248,7 +4248,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4438,7 +4438,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4628,7 +4628,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4818,7 +4818,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5008,7 +5008,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5394,20 +5394,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1"/>
-    <row r="100" spans="1:8" hidden="1"/>
-    <row r="101" spans="1:8" hidden="1"/>
-    <row r="102" spans="1:8" hidden="1"/>
-    <row r="103" spans="1:8" hidden="1"/>
-    <row r="104" spans="1:8" hidden="1"/>
-    <row r="105" spans="1:8" hidden="1"/>
-    <row r="106" spans="1:8" hidden="1"/>
-    <row r="107" spans="1:8" hidden="1"/>
-    <row r="108" spans="1:8" hidden="1"/>
-    <row r="109" spans="1:8" hidden="1"/>
-    <row r="110" spans="1:8" hidden="1"/>
-    <row r="111" spans="1:8" hidden="1"/>
-    <row r="112" spans="1:8" hidden="1">
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -5415,39 +5402,6 @@
         <v>34</v>
       </c>
     </row>
-    <row r="113" hidden="1"/>
-    <row r="114" hidden="1"/>
-    <row r="115" hidden="1"/>
-    <row r="116" hidden="1"/>
-    <row r="117" hidden="1"/>
-    <row r="118" hidden="1"/>
-    <row r="119" hidden="1"/>
-    <row r="120" hidden="1"/>
-    <row r="121" hidden="1"/>
-    <row r="122" hidden="1"/>
-    <row r="123" hidden="1"/>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1"/>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1"/>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1"/>
-    <row r="130" hidden="1"/>
-    <row r="131" hidden="1"/>
-    <row r="132" hidden="1"/>
-    <row r="133" hidden="1"/>
-    <row r="134" hidden="1"/>
-    <row r="135" hidden="1"/>
-    <row r="136" hidden="1"/>
-    <row r="137" hidden="1"/>
-    <row r="138" hidden="1"/>
-    <row r="139" hidden="1"/>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1"/>
-    <row r="142" hidden="1"/>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1"/>
-    <row r="145" hidden="1"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C1:E98" name="Textbooks"/>
@@ -5455,8 +5409,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5471,7 +5425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5617,7 +5571,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" hidden="1" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>63</v>
       </c>
@@ -5684,7 +5638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5696,7 +5650,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5765,7 +5719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5834,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5903,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5972,7 +5926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6041,7 +5995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6110,7 +6064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6179,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6248,7 +6202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6261,7 +6215,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6330,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6399,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6468,7 +6422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6537,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6606,7 +6560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6675,7 +6629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6744,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6813,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6827,7 +6781,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6896,7 +6850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6965,7 +6919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7034,7 +6988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7103,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7172,7 +7126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7241,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7310,7 +7264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7379,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7448,7 +7402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7462,7 +7416,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7531,7 +7485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7600,7 +7554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7669,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7738,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7807,7 +7761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7876,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7945,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8014,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8083,7 +8037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8097,7 +8051,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8166,7 +8120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8235,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8304,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8373,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8442,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8511,7 +8465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8580,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8649,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8718,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8732,7 +8686,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8801,7 +8755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8870,7 +8824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8939,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9008,7 +8962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9077,7 +9031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9146,7 +9100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9215,7 +9169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9284,7 +9238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9353,7 +9307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9367,7 +9321,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9436,7 +9390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9505,7 +9459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9574,7 +9528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="66" spans="1:27" ht="19.149999999999999">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9643,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9712,7 +9666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9781,7 +9735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9850,7 +9804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9919,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9988,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10002,7 +9956,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10071,7 +10025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10140,7 +10094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10209,7 +10163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10278,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10347,7 +10301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="78" spans="1:27" ht="19.149999999999999">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10416,7 +10370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10485,7 +10439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10554,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10623,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10637,7 +10591,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10706,7 +10660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10775,7 +10729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10844,7 +10798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10913,7 +10867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10982,7 +10936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11051,7 +11005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11120,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="90" spans="1:27" ht="19.149999999999999">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11189,7 +11143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11258,7 +11212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11272,7 +11226,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11341,7 +11295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11410,7 +11364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11479,7 +11433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11548,7 +11502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11617,7 +11571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11686,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11755,7 +11709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11824,7 +11778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11893,7 +11847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12487,7 +12441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12498,7 +12452,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12560,7 +12514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="113" spans="1:27" ht="19.149999999999999">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12622,7 +12576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="114" spans="1:27" ht="19.149999999999999">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12684,7 +12638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="115" spans="1:27" ht="19.149999999999999">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12746,7 +12700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="116" spans="1:27" ht="19.149999999999999">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12808,7 +12762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="117" spans="1:27" ht="19.149999999999999">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12870,7 +12824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="118" spans="1:27" ht="19.149999999999999">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12932,7 +12886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="119" spans="1:27" ht="19.149999999999999">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12994,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="120" spans="1:27" ht="19.149999999999999">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13056,7 +13010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="121" spans="1:27" ht="19.149999999999999">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13118,7 +13072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="122" spans="1:27" ht="19.149999999999999">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13180,7 +13134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="123" spans="1:27" ht="19.149999999999999">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13242,7 +13196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="124" spans="1:27" ht="19.149999999999999">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13304,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="125" spans="1:27" ht="19.149999999999999">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13366,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="126" spans="1:27" ht="19.149999999999999">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13428,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="127" spans="1:27" ht="19.149999999999999">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13485,186 +13439,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13684,8 +13458,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13703,7 +13477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13849,7 +13623,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="3" spans="1:27" ht="19.149999999999999">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13918,7 +13692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" ht="19.149999999999999">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13987,7 +13761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14056,7 +13830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14125,7 +13899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14194,7 +13968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14263,7 +14037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14332,7 +14106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14401,8 +14175,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14471,7 +14245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14540,7 +14314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14609,7 +14383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14678,7 +14452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14747,7 +14521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14816,7 +14590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14885,7 +14659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14954,8 +14728,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15024,7 +14798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15093,7 +14867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15162,7 +14936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15231,7 +15005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15300,7 +15074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15369,7 +15143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15438,7 +15212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15507,7 +15281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15576,8 +15350,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15646,7 +15420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15715,7 +15489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15784,7 +15558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15853,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15922,7 +15696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15991,7 +15765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16060,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16129,7 +15903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16198,7 +15972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16267,7 +16041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16336,8 +16110,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16406,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16475,7 +16249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16544,7 +16318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16613,7 +16387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16682,7 +16456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16751,7 +16525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16820,7 +16594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16889,7 +16663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16958,7 +16732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17027,7 +16801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17096,8 +16870,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17166,7 +16940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17235,7 +17009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17304,7 +17078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17373,7 +17147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17442,7 +17216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17511,7 +17285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17580,7 +17354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17649,7 +17423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17718,7 +17492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17787,7 +17561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17856,8 +17630,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17926,7 +17700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17995,7 +17769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18064,7 +17838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18133,7 +17907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18202,7 +17976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" ht="19.149999999999999">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18271,7 +18045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18340,7 +18114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18409,7 +18183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18478,7 +18252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18547,7 +18321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18616,8 +18390,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18686,7 +18460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18755,7 +18529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18824,7 +18598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" ht="19.149999999999999">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18893,7 +18667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18962,7 +18736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19031,7 +18805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19100,7 +18874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19169,7 +18943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19238,7 +19012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19307,7 +19081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19376,8 +19150,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19446,7 +19220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" ht="19.149999999999999">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19515,7 +19289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19584,7 +19358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19653,7 +19427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19722,7 +19496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19791,7 +19565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19860,7 +19634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19929,7 +19703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19998,7 +19772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20067,7 +19841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20136,8 +19910,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="19.149999999999999">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20206,7 +19980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20275,7 +20049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20344,7 +20118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20413,7 +20187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="107" spans="1:27" ht="19.149999999999999">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20482,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20551,7 +20325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="109" spans="1:27" ht="19.149999999999999">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20620,7 +20394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="110" spans="1:27" ht="19.149999999999999">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20689,7 +20463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="111" spans="1:27" ht="19.149999999999999">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20758,7 +20532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20827,7 +20601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999" hidden="1">
+    <row r="113" spans="1:28" ht="19.149999999999999">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20896,7 +20670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" hidden="1"/>
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
@@ -21526,8 +21300,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1" hidden="1"/>
-    <row r="124" spans="1:28" hidden="1">
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="124" spans="1:28">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21557,7 +21331,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28" hidden="1">
+    <row r="125" spans="1:28">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21587,7 +21361,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28" hidden="1">
+    <row r="126" spans="1:28">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21617,7 +21391,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28" hidden="1">
+    <row r="127" spans="1:28">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21647,7 +21421,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28" hidden="1">
+    <row r="128" spans="1:28">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21677,7 +21451,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28" hidden="1">
+    <row r="129" spans="1:28">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21707,7 +21481,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28" hidden="1">
+    <row r="130" spans="1:28">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21737,7 +21511,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28" hidden="1">
+    <row r="131" spans="1:28">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21767,7 +21541,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28" hidden="1">
+    <row r="132" spans="1:28">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21797,7 +21571,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28" hidden="1">
+    <row r="133" spans="1:28">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21827,7 +21601,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28" hidden="1">
+    <row r="134" spans="1:28">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21857,7 +21631,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28" hidden="1">
+    <row r="135" spans="1:28">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21887,7 +21661,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28" hidden="1">
+    <row r="136" spans="1:28">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21917,7 +21691,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28" hidden="1">
+    <row r="137" spans="1:28">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21947,7 +21721,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28" hidden="1">
+    <row r="138" spans="1:28">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21977,7 +21751,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28" hidden="1">
+    <row r="139" spans="1:28">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22007,7 +21781,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28" hidden="1">
+    <row r="140" spans="1:28">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -22037,186 +21811,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22234,8 +21828,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
